--- a/outputs/daily/hr_rankings_2026-06-20_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-06-20_full.xlsx
@@ -3264,7 +3264,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>40.3</v>
+        <v>37.8</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 1 HR</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6031,47 +6031,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>665019</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-21T02:10:00Z</t>
+          <t>2026-06-20T17:35:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>668678</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6094,62 +6094,58 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>52.4</v>
+        <v>43.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>57.3</v>
+        <v>39.4</v>
       </c>
       <c r="R21" t="n">
-        <v>28.2</v>
+        <v>84.7</v>
       </c>
       <c r="S21" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6169,134 +6165,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 5/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.7% barrel, 18.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>101.6676</t>
+          <t>100.9649</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4559</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2041</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3492</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>73.82</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>43.28</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>0.2062</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4725</t>
+          <t>0.3812</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1892</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>28.69</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="inlineStr"/>
+          <t>26.41</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6307,47 +6311,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>665019</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Kody Clemens</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-20T17:35:00Z</t>
+          <t>2026-06-21T02:10:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>668678</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6356,7 +6360,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6370,58 +6374,62 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>43.4</v>
+        <v>52.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>39.4</v>
+        <v>57.3</v>
       </c>
       <c r="R22" t="n">
-        <v>84.7</v>
+        <v>28.2</v>
       </c>
       <c r="S22" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>80</v>
       </c>
       <c r="U22" t="n">
-        <v>24.9</v>
+        <v>60</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6441,142 +6449,134 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/14, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 11.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.7% barrel, 18.4 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>12.56</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>100.9649</t>
+          <t>101.6676</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0.4559</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.2041</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3492</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>43.28</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.2062</t>
+          <t>0.228</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>44.54</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.3812</t>
+          <t>0.4725</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.1892</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>26.41</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+          <t>28.69</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/17, 1 HR</t>
+          <t>Last 7 games: 1/18, 1 HR</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
@@ -18872,7 +18872,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>50</v>
       </c>
       <c r="U75" t="n">
-        <v>76.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -25832,7 +25832,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -34022,7 +34022,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -34032,7 +34032,7 @@
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/17, 0 HR</t>
+          <t>Last 7 games: 0/18, 0 HR</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
@@ -34188,7 +34188,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -38360,7 +38360,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -39476,7 +39476,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -41704,7 +41704,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -55028,7 +55028,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -71146,7 +71146,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -72538,7 +72538,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -72842,7 +72842,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -72875,7 +72875,7 @@
         <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>40.3</v>
+        <v>37.8</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -72932,7 +72932,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -72942,7 +72942,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 1 HR</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -73378,7 +73378,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -73913,47 +73913,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>665019</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-21T02:10:00Z</t>
+          <t>2026-06-20T17:35:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>668678</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -73962,7 +73962,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -73976,62 +73976,58 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>52.4</v>
+        <v>43.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>57.3</v>
+        <v>39.4</v>
       </c>
       <c r="R21" t="n">
-        <v>28.2</v>
+        <v>84.7</v>
       </c>
       <c r="S21" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -74051,134 +74047,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 5/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.7% barrel, 18.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>101.6676</t>
+          <t>100.9649</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4559</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2041</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3492</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>73.82</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>43.28</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>0.2062</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4725</t>
+          <t>0.3812</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1892</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>28.69</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="inlineStr"/>
+          <t>26.41</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
